--- a/POTAL_D9_Customer_Acquisition.xlsx
+++ b/POTAL_D9_Customer_Acquisition.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="글로벌캠페인_CW19" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ColdEmail_2603260905" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="콜드이메일" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enterprise Leads" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Hunt" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMB 100 타겟" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D9 Dashboard" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cold Email Campaign 1" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outreach_Log" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="CW21_20260328" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="글로벌캠페인_CW19" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leads" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ColdEmail_2603260905" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="콜드이메일" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Enterprise Leads" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Product Hunt" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="SMB 100 타겟" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="D9 Dashboard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Cold Email Campaign 1" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Outreach_Log" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -571,406 +572,122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>국가</t>
-        </is>
-      </c>
-      <c r="B1" s="19" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="C1" s="19" t="inlineStr">
-        <is>
-          <t>기업수</t>
-        </is>
-      </c>
-      <c r="D1" s="19" t="inlineStr">
-        <is>
-          <t>업종 분포</t>
-        </is>
-      </c>
-      <c r="E1" s="19" t="inlineStr">
-        <is>
-          <t>이메일 검증상태</t>
-        </is>
-      </c>
-      <c r="F1" s="19" t="inlineStr">
-        <is>
-          <t>Gmail드래프트</t>
-        </is>
-      </c>
-      <c r="G1" s="19" t="inlineStr">
-        <is>
-          <t>비고</t>
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>시간</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>영향</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="B2" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="20" t="n">
-        <v>100</v>
-      </c>
-      <c r="D2" s="21" t="inlineStr">
-        <is>
-          <t>dropshipping, B2B marketplace, logistics, payment, SaaS, purchasing agents, brands</t>
-        </is>
-      </c>
-      <c r="E2" s="20" t="inlineStr">
-        <is>
-          <t>✅완료 (84검증/16 NOT_FOUND)</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>미생성</t>
-        </is>
-      </c>
-      <c r="G2" s="20" t="inlineStr">
-        <is>
-          <t>CW20 검증 완료</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>v3 파이프라인 완성</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>21/21 Section, 595 codified rules, 22/22 PASS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>분류 정확도 100% → 고객 신뢰 기반</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="20" t="n">
-        <v>100</v>
-      </c>
-      <c r="D3" s="21" t="inlineStr">
-        <is>
-          <t>customs/Brexit, logistics, payments, VAT, ecommerce_ops, fulfilment, freight, marketing</t>
-        </is>
-      </c>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>✅완료 (45검증/44 NOT_FOUND)</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>95건(미검증주소)</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="inlineStr">
-        <is>
-          <t>CW20 검증 완료</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>field-validator 개선</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PLATFORM_TERMS +40 키워드 → 400 에러 감소</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>API 사용자 온보딩 장벽 낮춤</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>SG</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>logistics, payment, marketplace, fulfilment, trade_compliance</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="inlineStr">
-        <is>
-          <t>✅완료 (14검증/11 NOT_FOUND)</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>23건(미검증주소)</t>
-        </is>
-      </c>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>CW20 검증 완료</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S21 미술품 분류</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ch.97 9701-9706 heading hints 추가</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>미술품/골동품 셀러 대응 가능</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>logistics, payment, crossborder_marketplace, shipping, fulfilment</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>✅완료 (14검증/11 NOT_FOUND)</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>미생성</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>CW20 검증 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>logistics, shipping, payment, warehouse, fulfilment, marketplace</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>✅완료 (17검증/8 NOT_FOUND)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>미생성</t>
-        </is>
-      </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>CW20 검증 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>crossborder_platform, fraud_prevention, payment, delivery_tech, ecommerce_ai</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>✅완료 (15검증/10 NOT_FOUND)</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>미생성</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>CW20 검증 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>logistics, ecommerce, marketplace_saas, ecommerce_ops, tax_compliance, payment</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>✅완료 (27검증/7 NOT_FOUND)</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>미생성</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>CW20 검증 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>logistics, shipping, ecommerce_platform, payment, trade_compliance, freight</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>✅완료 (13검증/20 NOT_FOUND)</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>미생성</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>CW20 검증 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>UAE</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>logistics, ecommerce, payment, freight, b2b_marketplace, port_logistics</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>✅완료 (22검증/12 NOT_FOUND)</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>미생성</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>CW20 검증 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="C11" s="12">
-        <f>SUM(C2:C10)</f>
-        <v/>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>✅전체완료 (251검증/139 NOT_FOUND)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-03-28 12:01 KST</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>캠페인 현황 (2026-03-28 15:00 KST)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1차 발송 완료: 67건 (이전 세션)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>핫리드: Calcurates CEO (Nikolay), Easyship (전문팀 검토)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>글로벌 캠페인: ~400개 기업 리스트 생성 완료, 이메일 검증 진행 중</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>다음: 검증 완료 후 국가별/업종별 개인화 이메일 Gmail 드래프트 생성</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>외장하드 데이터 대조</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>14개 규칙파일 + 97 conflict patterns 100% 검증</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>데이터 완전성 증명 가능</t>
         </is>
       </c>
     </row>
@@ -980,6 +697,285 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>시간</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>활동</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>상세</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>결과</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-25 20:00</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>타겟 리서치</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>크로스보더 100사 CSV 작성 (ecom_tools 56, logistics 39, payment 4, beauty 1)</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>67개 유효 이메일 확인</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-25 20:20</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>콘텐츠 업데이트</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>콜드이메일 EN/KR 업데이트: 100% HS정확도, 9-field, 592 GRI, 131K tariff lines</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>cold-email-final.md 반영</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-25 20:25</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>콘텐츠 수정</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>비교차트 허위 문구 제거 ("2,000+ businesses" → 정확한 문구)</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>comparison-chart.html 수정</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-25 20:40</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Gmail 드래프트</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>67개 타겟사에 개인화 콜드이메일 Gmail 드래프트 생성</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>67/67 완료</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-25 22:30</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>발송 준비</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>은태님 검토 후 10-20개씩 순차 발송 예정 (스팸 방지)</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>대기중</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>캠페인 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>총 타겟</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>유효 이메일</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gmail 드래프트</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>67/67 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>국가 분포</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>US 46, UK 11, CA 6, IN 5, SG 3, 기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ecom_tools 56, logistics 39, payment 4, beauty 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>발송 상태</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>은태님 검토 후 발송 예정</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1560,6 +1556,419 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>국가</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>기업수</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>업종 분포</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>이메일 검증상태</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>Gmail드래프트</t>
+        </is>
+      </c>
+      <c r="G1" s="19" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>dropshipping, B2B marketplace, logistics, payment, SaaS, purchasing agents, brands</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>✅완료 (84검증/16 NOT_FOUND)</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>미생성</t>
+        </is>
+      </c>
+      <c r="G2" s="20" t="inlineStr">
+        <is>
+          <t>CW20 검증 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>customs/Brexit, logistics, payments, VAT, ecommerce_ops, fulfilment, freight, marketing</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>✅완료 (45검증/44 NOT_FOUND)</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>95건(미검증주소)</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>CW20 검증 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>logistics, payment, marketplace, fulfilment, trade_compliance</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>✅완료 (14검증/11 NOT_FOUND)</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>23건(미검증주소)</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>CW20 검증 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>logistics, payment, crossborder_marketplace, shipping, fulfilment</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>✅완료 (14검증/11 NOT_FOUND)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>미생성</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>CW20 검증 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>logistics, shipping, payment, warehouse, fulfilment, marketplace</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>✅완료 (17검증/8 NOT_FOUND)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>미생성</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>CW20 검증 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>crossborder_platform, fraud_prevention, payment, delivery_tech, ecommerce_ai</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>✅완료 (15검증/10 NOT_FOUND)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>미생성</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>CW20 검증 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>logistics, ecommerce, marketplace_saas, ecommerce_ops, tax_compliance, payment</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>✅완료 (27검증/7 NOT_FOUND)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>미생성</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>CW20 검증 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>logistics, shipping, ecommerce_platform, payment, trade_compliance, freight</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>✅완료 (13검증/20 NOT_FOUND)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>미생성</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>CW20 검증 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>logistics, ecommerce, payment, freight, b2b_marketplace, port_logistics</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>✅완료 (22검증/12 NOT_FOUND)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>미생성</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>CW20 검증 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C11" s="12">
+        <f>SUM(C2:C10)</f>
+        <v/>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>✅전체완료 (251검증/139 NOT_FOUND)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-03-28 12:01 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>캠페인 현황 (2026-03-28 15:00 KST)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1차 발송 완료: 67건 (이전 세션)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>핫리드: Calcurates CEO (Nikolay), Easyship (전문팀 검토)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>글로벌 캠페인: ~400개 기업 리스트 생성 완료, 이메일 검증 진행 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>다음: 검증 완료 후 국가별/업종별 개인화 이메일 Gmail 드래프트 생성</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1878,7 +2287,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2743,7 +3152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2875,7 +3284,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2953,7 +3362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3139,7 +3548,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3212,7 +3621,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3369,14 +3778,6 @@
       </c>
       <c r="D7" s="2" t="inlineStr"/>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
@@ -3403,285 +3804,6 @@
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>✅</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>순번</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>시간</t>
-        </is>
-      </c>
-      <c r="C1" s="9" t="inlineStr">
-        <is>
-          <t>활동</t>
-        </is>
-      </c>
-      <c r="D1" s="9" t="inlineStr">
-        <is>
-          <t>상세</t>
-        </is>
-      </c>
-      <c r="E1" s="9" t="inlineStr">
-        <is>
-          <t>결과</t>
-        </is>
-      </c>
-      <c r="F1" s="9" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-25 20:00</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>타겟 리서치</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>크로스보더 100사 CSV 작성 (ecom_tools 56, logistics 39, payment 4, beauty 1)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>67개 유효 이메일 확인</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-25 20:20</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>콘텐츠 업데이트</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>콜드이메일 EN/KR 업데이트: 100% HS정확도, 9-field, 592 GRI, 131K tariff lines</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>cold-email-final.md 반영</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-25 20:25</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>콘텐츠 수정</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>비교차트 허위 문구 제거 ("2,000+ businesses" → 정확한 문구)</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>comparison-chart.html 수정</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-25 20:40</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Gmail 드래프트</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>67개 타겟사에 개인화 콜드이메일 Gmail 드래프트 생성</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>67/67 완료</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-25 22:30</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>발송 준비</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>은태님 검토 후 10-20개씩 순차 발송 예정 (스팸 방지)</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>대기중</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>⏳</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>캠페인 요약</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>총 타겟</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>유효 이메일</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Gmail 드래프트</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>67/67 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>국가 분포</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>US 46, UK 11, CA 6, IN 5, SG 3, 기타</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ecom_tools 56, logistics 39, payment 4, beauty 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>발송 상태</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>은태님 검토 후 발송 예정</t>
         </is>
       </c>
     </row>

--- a/POTAL_D9_Customer_Acquisition.xlsx
+++ b/POTAL_D9_Customer_Acquisition.xlsx
@@ -7,17 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CW21_20260328" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="글로벌캠페인_CW19" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leads" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ColdEmail_2603260905" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="콜드이메일" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Enterprise Leads" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Product Hunt" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="SMB 100 타겟" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="D9 Dashboard" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Cold Email Campaign 1" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Outreach_Log" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="CW22B_SignupFlow" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CW21_20260328" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="글로벌캠페인_CW19" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leads" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ColdEmail_2603260905" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="콜드이메일" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Enterprise Leads" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Product Hunt" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SMB 100 타겟" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="D9 Dashboard" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Cold Email Campaign 1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Outreach_Log" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -572,122 +573,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>시간</t>
+          <t>항목</t>
         </is>
       </c>
       <c r="B1" s="12" t="inlineStr">
         <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="C1" s="12" t="inlineStr">
-        <is>
           <t>내용</t>
-        </is>
-      </c>
-      <c r="D1" s="12" t="inlineStr">
-        <is>
-          <t>영향</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-28 23:30 KST</t>
+          <t>날짜</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>v3 파이프라인 완성</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>21/21 Section, 595 codified rules, 22/22 PASS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>분류 정확도 100% → 고객 신뢰 기반</t>
+          <t>2026-03-29 21:00~22:10 KST</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-28 23:30 KST</t>
+          <t>작업</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>field-validator 개선</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PLATFORM_TERMS +40 키워드 → 400 에러 감소</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>API 사용자 온보딩 장벽 낮춤</t>
+          <t>가입 플로우 개선 — Google OAuth + 이메일 인증</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-28 23:30 KST</t>
+          <t>Google OAuth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S21 미술품 분류</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ch.97 9701-9706 heading hints 추가</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>미술품/골동품 셀러 대응 가능</t>
+          <t>가입 후 /auth/complete-profile에서 회사명/국가/업종 필수 입력 강제</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-28 23:30 KST</t>
+          <t>이메일 가입</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>외장하드 데이터 대조</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>14개 규칙파일 + 97 conflict patterns 100% 검증</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>데이터 완전성 증명 가능</t>
+          <t>supabase.auth.signUp() → Supabase 인증 이메일 발송 → 링크 클릭 후 seller+API키 자동 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FreeBanner</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>제거 (히어로 '140 Features. All Free. Forever.'와 중복)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>기대 효과</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>가입 전환율 개선 (인증 프로세스 정상화), OAuth 사용자 프로필 수집률 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>커밋</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>a62f385, d883f0a, 9f0e5b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>✅ 완료 + Chrome MCP 테스트 통과</t>
         </is>
       </c>
     </row>
@@ -697,6 +694,197 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>수치</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>마지막업데이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>콜드이메일 발송</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>글로벌 251개 검증 완료, 드래프트 생성 중</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>콜드이메일 응답</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>3건 (Calcurates🔥/Razorpay/Mollie)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Leads</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1건 (DB)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Product Hunt</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>런치 완료 (3/28)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>유료 고객</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>0명</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>MRR</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>\/bin/bash</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>최근 활동 로그</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:30</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Division 로그 체계 구축 — D9 엑셀 + CLAUDE.md 규칙 + 매일 자동 점검 스케줄 설정 완료</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Cowork CW18 13차</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -975,7 +1163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1556,6 +1744,136 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>시간</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>v3 파이프라인 완성</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>21/21 Section, 595 codified rules, 22/22 PASS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>분류 정확도 100% → 고객 신뢰 기반</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>field-validator 개선</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PLATFORM_TERMS +40 키워드 → 400 에러 감소</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>API 사용자 온보딩 장벽 낮춤</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S21 미술품 분류</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ch.97 9701-9706 heading hints 추가</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>미술품/골동품 셀러 대응 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>외장하드 데이터 대조</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>14개 규칙파일 + 97 conflict patterns 100% 검증</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>데이터 완전성 증명 가능</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1968,7 +2286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2287,7 +2605,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3152,7 +3470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3284,7 +3602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3362,7 +3680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3548,7 +3866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3619,195 +3937,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>수치</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>마지막업데이트</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>콜드이메일 발송</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>글로벌 251개 검증 완료, 드래프트 생성 중</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>콜드이메일 응답</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>3건 (Calcurates🔥/Razorpay/Mollie)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise Leads</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>1건 (DB)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>⏳</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Product Hunt</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>런치 완료 (3/28)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>유료 고객</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>0명</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>MRR</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>\/bin/bash</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>최근 활동 로그</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-25 19:30</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Division 로그 체계 구축 — D9 엑셀 + CLAUDE.md 규칙 + 매일 자동 점검 스케줄 설정 완료</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Cowork CW18 13차</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/POTAL_D9_Customer_Acquisition.xlsx
+++ b/POTAL_D9_Customer_Acquisition.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CW22B_SignupFlow" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CW21_20260328" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="글로벌캠페인_CW19" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leads" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ColdEmail_2603260905" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="콜드이메일" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Enterprise Leads" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Product Hunt" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SMB 100 타겟" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="D9 Dashboard" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Cold Email Campaign 1" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Outreach_Log" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CW22D_BigCommerce" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CW22B_SignupFlow" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CW21_20260328" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="글로벌캠페인_CW19" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leads" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ColdEmail_2603260905" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="콜드이메일" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enterprise Leads" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Hunt" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMB 100 타겟" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D9 Dashboard" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cold Email Campaign 1" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outreach_Log" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +80,10 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="12">
@@ -158,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -208,6 +213,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -573,20 +579,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
@@ -600,7 +606,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-29 21:00~22:10 KST</t>
+          <t>2026-03-30 13:00 KST</t>
         </is>
       </c>
     </row>
@@ -612,79 +618,115 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>가입 플로우 개선 — Google OAuth + 이메일 인증</t>
+          <t>BigCommerce Technology Partner Program 가입 시도 및 파트너팀 이메일 발송</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Google OAuth</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>가입 후 /auth/complete-profile에서 회사명/국가/업종 필수 입력 강제</t>
+          <t>⏳ 파트너팀 답장 대기</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>이메일 가입</t>
+          <t>시도1_이메일</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>supabase.auth.signUp() → Supabase 인증 이메일 발송 → 링크 클릭 후 seller+API키 자동 생성</t>
+          <t>soulmaten7@gmail.com → ❌ "You cannot register with this e-mail address"</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FreeBanner</t>
+          <t>시도2_이메일</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>제거 (히어로 '140 Features. All Free. Forever.'와 중복)</t>
+          <t>contact@potal.app → ❌ 동일 오류 (도메인 신뢰도 or 이미 등록 이슈)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>기대 효과</t>
+          <t>해결방법</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>가입 전환율 개선 (인증 프로세스 정상화), OAuth 사용자 프로필 수집률 100%</t>
+          <t>partners@bigcommerce.com 직접 이메일 발송</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>커밋</t>
+          <t>이메일_제목</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>a62f385, d883f0a, 9f0e5b6</t>
+          <t>Technology Partner Program Registration Issue - POTAL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>이메일_내용</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>✅ 완료 + Chrome MCP 테스트 통과</t>
+          <t>Company: POTAL / Website: potal.app / App: Landed Cost Calculator / Contact: contact@potal.app</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>예상_응답</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1~3 영업일 내 수동 계정 생성 후 연락</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>다음단계</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>답장 수신 후 → DevTools 앱 생성 → OAuth callback URLs 설정 → Marketplace 제출</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>참고_URL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://partners.bigcommerce.com/English/register_email.aspx</t>
         </is>
       </c>
     </row>
@@ -694,6 +736,79 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>웹사이트</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>이메일</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>확인상태</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>발송상태</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>응답</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>data/cold_email_target_100_smb.csv 참조</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -884,7 +999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1163,7 +1278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1749,6 +1864,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-29 21:00~22:10 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>작업</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>가입 플로우 개선 — Google OAuth + 이메일 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Google OAuth</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>가입 후 /auth/complete-profile에서 회사명/국가/업종 필수 입력 강제</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>이메일 가입</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>supabase.auth.signUp() → Supabase 인증 이메일 발송 → 링크 클릭 후 seller+API키 자동 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FreeBanner</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>제거 (히어로 '140 Features. All Free. Forever.'와 중복)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>기대 효과</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>가입 전환율 개선 (인증 프로세스 정상화), OAuth 사용자 프로필 수집률 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>커밋</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>a62f385, d883f0a, 9f0e5b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>✅ 완료 + Chrome MCP 테스트 통과</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1873,7 +2114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2286,7 +2527,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2605,7 +2846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3470,7 +3711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3602,7 +3843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3680,7 +3921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3864,77 +4105,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>순번</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>웹사이트</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>이메일</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>확인상태</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>발송상태</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>응답</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>data/cold_email_target_100_smb.csv 참조</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>